--- a/tests/realSuite/Piano-Viaggi-GdG_24-marzo-26-Def-con-Vettore-4/input.xlsx
+++ b/tests/realSuite/Piano-Viaggi-GdG_24-marzo-26-Def-con-Vettore-4/input.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,75 +436,45 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IC ARCO</t>
+          <t>IC ROVERETO EST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Arco, Ist. Comprensivo Arco, Località Prabi</t>
+          <t>Rovereto, Piazzale Orsi (di fronte Ist. Veronesi)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IC AVIO</t>
+          <t>IC TIONE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Avio, Viale Degasperi 69</t>
+          <t>Tione, Via Circonvalazione 44</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IC ROVERETO EST</t>
+          <t>IS S. SHOOL – Students staff</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Rovereto, Piazzale Orsi (di fronte Ist. Veronesi)</t>
+          <t>Trento, Park Ex Italcementi</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>IC TIONE</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Tione, Via Circonvalazione 44</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>IS S. SHOOL – Students staff</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Trento, Park Ex Italcementi</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
         <v>2</v>
       </c>
     </row>
